--- a/xlsx/单位/演员技能.xlsx
+++ b/xlsx/单位/演员技能.xlsx
@@ -780,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -789,9 +789,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1269,46 +1266,46 @@
       <c r="P3" s="1"/>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:16">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="4" t="b">
+      <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>1000</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>0</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>10</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>15</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="3">
         <v>0</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="3">
         <v>2</v>
       </c>
       <c r="O4" s="3"/>

--- a/xlsx/单位/演员技能.xlsx
+++ b/xlsx/单位/演员技能.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="技能演员.ts" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>自定义id
 &lt;%
@@ -127,13 +127,13 @@
     <t>attribute</t>
   </si>
   <si>
-    <t>一线光阴</t>
+    <t>沟壑</t>
   </si>
   <si>
     <t>技能</t>
   </si>
   <si>
-    <t>无目标</t>
+    <t>点</t>
   </si>
   <si>
     <t>${id}</t>
@@ -145,10 +145,10 @@
     <t>ReplaceableTextures\CommandButtons\BTNManaShield.blp</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
     <t>闪现</t>
-  </si>
-  <si>
-    <t>点</t>
   </si>
   <si>
     <t>能瞬间移动一段距离。</t>
@@ -1113,16 +1113,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.76363636363636" customWidth="1"/>
-    <col min="2" max="3" width="8.5" customWidth="1"/>
-    <col min="4" max="4" width="14.2090909090909" customWidth="1"/>
-    <col min="5" max="5" width="8.10909090909091" customWidth="1"/>
-    <col min="6" max="6" width="12.3545454545455" customWidth="1"/>
-    <col min="7" max="7" width="19.5181818181818" customWidth="1"/>
-    <col min="8" max="8" width="10.3636363636364" customWidth="1"/>
-    <col min="9" max="9" width="8.83636363636364" customWidth="1"/>
+    <col min="1" max="1" width="9.76666666666667" customWidth="1"/>
+    <col min="2" max="2" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="14.2083333333333" customWidth="1"/>
+    <col min="5" max="5" width="8.10833333333333" customWidth="1"/>
+    <col min="6" max="6" width="12.3583333333333" customWidth="1"/>
+    <col min="7" max="7" width="19.5166666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.3666666666667" customWidth="1"/>
+    <col min="9" max="9" width="8.83333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31" customHeight="1" spans="1:16">
@@ -1252,7 +1253,9 @@
       <c r="J3" s="3">
         <v>50</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L3" s="3">
         <v>15</v>
       </c>
@@ -1267,13 +1270,13 @@
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="b">
         <v>0</v>
